--- a/AAII_Financials/Quarterly/RL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>RL</t>
   </si>
@@ -656,541 +656,554 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E7" s="2">
         <v>46109</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46018</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45927</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45836</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45745</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45654</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45563</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45472</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45381</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45290</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45108</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45017</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44835</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44744</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44653</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44464</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44282</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44191</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44009</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43918</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43827</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43736</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43645</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43554</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43463</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43372</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43099</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42917</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42826</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1959800</v>
+      </c>
+      <c r="E8" s="3">
         <v>1978700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2406000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2010700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1719100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1697300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2143500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1726000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1512200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1567900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1934000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1633000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1496500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1540800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1832300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1579900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1490600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1522700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1815400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1504100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1376300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1287000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1432800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1193500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>487500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1274100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1750700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1706200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1428800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1505700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1725800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1690900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1390600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1529200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1641800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1664200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1347100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1565800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1714000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1821000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>515600</v>
+      </c>
+      <c r="E9" s="3">
         <v>599900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>724300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>644300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>476800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>532000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>677400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>570300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>446400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>524200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>648900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>564700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>466300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>588000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>637600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>559200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>477600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>556600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>617300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>492400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>416200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>477700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>495400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>399500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>137500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>678500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>661600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>656800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>507400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>600100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>663200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>661600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>494900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>614400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>645600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>667800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>495200</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>746700</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>731000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>867000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1444200</v>
+      </c>
+      <c r="E10" s="3">
         <v>1378800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1681700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1366400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1242300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1165300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1466100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1155700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1065800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1043700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1285100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1068300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1030200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>952800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1194700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1020700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1013000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>966100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1198100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1011700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>960100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>809300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>937400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>794000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>350000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>595600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1089100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1049400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>921400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>905600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1062600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1029300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>895700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>914800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>996200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>996400</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>851900</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>819100</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>983000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>954000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1233,8 +1246,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1355,8 +1369,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1477,219 +1494,225 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E14" s="3">
         <v>-56400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>31000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>37300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
+        <v>17400</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="J14" s="3">
+        <v>10000</v>
+      </c>
+      <c r="K14" s="3">
+        <v>18400</v>
+      </c>
+      <c r="L14" s="3">
+        <v>2300</v>
+      </c>
+      <c r="M14" s="3">
+        <v>24400</v>
+      </c>
+      <c r="N14" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="O14" s="3">
+        <v>7200</v>
+      </c>
+      <c r="P14" s="3">
+        <v>28600</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>28800</v>
+      </c>
+      <c r="R14" s="3">
+        <v>11800</v>
+      </c>
+      <c r="S14" s="3">
+        <v>4700</v>
+      </c>
+      <c r="T14" s="3">
+        <v>14800</v>
+      </c>
+      <c r="U14" s="3">
         <v>5800</v>
       </c>
-      <c r="H14" s="3">
-        <v>-8500</v>
-      </c>
-      <c r="I14" s="3">
-        <v>10000</v>
-      </c>
-      <c r="J14" s="3">
-        <v>18400</v>
-      </c>
-      <c r="K14" s="3">
-        <v>2300</v>
-      </c>
-      <c r="L14" s="3">
-        <v>24400</v>
-      </c>
-      <c r="M14" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="N14" s="3">
-        <v>7200</v>
-      </c>
-      <c r="O14" s="3">
-        <v>28600</v>
-      </c>
-      <c r="P14" s="3">
-        <v>28800</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>11800</v>
-      </c>
-      <c r="R14" s="3">
-        <v>4700</v>
-      </c>
-      <c r="S14" s="3">
-        <v>14800</v>
-      </c>
-      <c r="T14" s="3">
-        <v>5800</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-1300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>9600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>3900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>18500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>198100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>22500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>24500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>17700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>16400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>29100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>68300</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>45400</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>25700</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>23700</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>60800</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>27200</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>30400</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>47200</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>321400</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>77000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>69000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>58900</v>
+      </c>
+      <c r="E15" s="3">
         <v>-140800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>59700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>57000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>55500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>-131500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>54300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>55900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>54400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>34000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>53000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>55200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>58300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-115900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>51700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>49600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>51400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>29700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>51800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>51500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>52700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>57500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>55100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>56300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>58500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>4700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>4500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>4700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>4200</v>
-      </c>
-      <c r="AF15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG15" s="3" t="s">
         <v>8</v>
@@ -1703,8 +1726,8 @@
       <c r="AJ15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK15" s="3">
-        <v>6000</v>
+      <c r="AK15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AL15" s="3">
         <v>6000</v>
@@ -1713,16 +1736,19 @@
         <v>6000</v>
       </c>
       <c r="AN15" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AO15" s="3">
         <v>75500</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>78000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>76000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1762,252 +1788,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1599300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1714100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1922600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1727700</v>
       </c>
-      <c r="G17" s="3">
-        <v>1439700</v>
-      </c>
       <c r="H17" s="3">
+        <v>1428100</v>
+      </c>
+      <c r="I17" s="3">
         <v>1549900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1743800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1528700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1301400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1447000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1621200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1461300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1301500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1637300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1550200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1373200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1315400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1485900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1526300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1252200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1155700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1312700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1262400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1213800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>655500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1557900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1526300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1473100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1285500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1477800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1532000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1480900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1260500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1503800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1452600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1470900</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1256800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1833600</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1586000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1745000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>360500</v>
+      </c>
+      <c r="E18" s="3">
         <v>264600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>483400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>283000</v>
       </c>
-      <c r="G18" s="3">
-        <v>279400</v>
-      </c>
       <c r="H18" s="3">
+        <v>291000</v>
+      </c>
+      <c r="I18" s="3">
         <v>147400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>399700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>197300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>210800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>120900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>312800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>171700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>195000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-96500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>282100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>206700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>175200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>36800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>289100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>251900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>220600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-25700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>170400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-20300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-168000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-283800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>224400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>233100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>143300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>27900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>193800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>210000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>130100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>25400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>189200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>193300</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>90300</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>-267800</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>128000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>76000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2050,618 +2083,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E20" s="3">
         <v>126800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-12800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>12200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>4800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-168200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>10300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>6200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>4300</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>4000</v>
       </c>
       <c r="Z20" s="3">
         <v>4000</v>
       </c>
       <c r="AA20" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AB20" s="3">
         <v>7700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>5900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>14900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>12700</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>12500</v>
       </c>
       <c r="AF20" s="3">
         <v>12500</v>
       </c>
       <c r="AG20" s="3">
+        <v>12500</v>
+      </c>
+      <c r="AH20" s="3">
         <v>10900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>10800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>7200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>3300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>1900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>2500</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>1500</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>300</v>
       </c>
-      <c r="AO20" s="3">
-        <v>0</v>
-      </c>
       <c r="AP20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>425000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>555900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>338400</v>
       </c>
-      <c r="G21" s="3">
-        <v>336000</v>
-      </c>
       <c r="H21" s="3">
+        <v>347600</v>
+      </c>
+      <c r="I21" s="3">
         <v>14300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>441800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>255900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>264100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>160700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>367800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>222100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>251800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-44200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>347600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>262900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>228800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>103400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>346800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>307600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>280500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>40700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>234700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>45200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-96600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-209400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>307500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>312400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>222000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>109700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>276700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>290500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>207600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>104500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>263800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>269600</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>164700</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>-192000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>206000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>153000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E22" s="3">
         <v>13500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>13300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>15900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>11500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>10200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>11600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>11400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>10900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>11600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>10600</v>
-      </c>
-      <c r="N22" s="3">
-        <v>10000</v>
       </c>
       <c r="O22" s="3">
         <v>10000</v>
       </c>
       <c r="P22" s="3">
+        <v>10000</v>
+      </c>
+      <c r="Q22" s="3">
         <v>7100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>12000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>9500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>11800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>13700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>13400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>13600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>13300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>13900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>12200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>12800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>12300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>9300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>8900</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>9200</v>
       </c>
       <c r="AE22" s="3">
         <v>9200</v>
       </c>
       <c r="AF22" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AG22" s="3">
         <v>5100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>5200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>6000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>4400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>3800</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>4800</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>4600</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>5000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>1400</v>
-      </c>
-      <c r="AO22" s="3">
-        <v>4000</v>
       </c>
       <c r="AP22" s="3">
         <v>4000</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>4000</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>342200</v>
+      </c>
+      <c r="E23" s="3">
         <v>193100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>463800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>242800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>278000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>162300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>383700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>188100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>216600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>111500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>329800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>165500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>170600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>49200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>280400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>200100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>162200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>29300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>277200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>238100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>210000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-35300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>162200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-29100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-172600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-287200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>230400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>236600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>146600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>35300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>199500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>214800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>132900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>24900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>186300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>191200</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>86800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-268900</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>124000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>73000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E24" s="3">
         <v>41500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>102200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>35300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>57600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>33300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>86300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>40200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>48000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>20800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>53200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>18600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>38500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>16900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>63900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>49600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>38800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>59500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>44800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>45300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>39200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>28200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>10000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-44900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>87100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-103700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>54500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>29500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-23900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>79500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>44500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>23900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-6500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>36800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>47400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>27300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>-64600</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>42000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>28000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2782,252 +2831,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>262200</v>
+      </c>
+      <c r="E26" s="3">
         <v>151600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>361600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>207500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>220400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>129000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>297400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>147900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>168600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>90700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>276600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>146900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>132100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>32300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>216500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>150500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>123400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>24400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>217700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>193300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>164700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-74500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>134000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-39100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-127700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-374300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>334100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>182100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>117100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>59200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>120000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>170300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>109000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>31400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>149500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>143800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>59500</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-204300</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>82000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>45000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>262200</v>
+      </c>
+      <c r="E27" s="3">
         <v>151600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>361600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>207500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>220400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>129000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>297400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>147900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>168600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>90700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>276600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>146900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>132100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>32300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>216500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>150500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>123400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>24400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>217700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>193300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>164700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-74500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>134000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-39100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-127700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-374300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>334100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>182100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>117100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>59200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>120000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>170300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>109000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>31400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>149500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>143800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>59500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-204300</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>82000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>45000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3148,8 +3206,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3195,8 +3256,8 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
@@ -3213,23 +3274,23 @@
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
         <v>400</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-14200</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>125300</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -3237,11 +3298,11 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-27600</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -3249,14 +3310,14 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3">
         <v>9900</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-231300</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3270,8 +3331,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3392,8 +3456,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3514,252 +3581,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-126800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>12800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-12200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-4800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>168200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-10300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-6200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-4300</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-4000</v>
       </c>
       <c r="Z32" s="3">
         <v>-4000</v>
       </c>
       <c r="AA32" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-5900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-14900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-12700</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>-12500</v>
       </c>
       <c r="AF32" s="3">
         <v>-12500</v>
       </c>
       <c r="AG32" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-10900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-10800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-7200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-3300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-1900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-2500</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-300</v>
       </c>
-      <c r="AO32" s="3">
-        <v>0</v>
-      </c>
       <c r="AP32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>262200</v>
+      </c>
+      <c r="E33" s="3">
         <v>151600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>361600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>207500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>220400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>129000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>297400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>147900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>168600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>90700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>276600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>146900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>132100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>32300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>216500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>150500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>123400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>24400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>217700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>193300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>164700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-74100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>119800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-39100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-127700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-249000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>334100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>182100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>117100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>31600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>120000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>170300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>109000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>41300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-81800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>143800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>59500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-204300</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>82000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>45000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3880,257 +3956,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>262200</v>
+      </c>
+      <c r="E35" s="3">
         <v>151600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>361600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>207500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>220400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>129000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>297400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>147900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>168600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>90700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>276600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>146900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>132100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>32300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>216500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>150500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>123400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>24400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>217700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>193300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>164700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-74100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>119800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-39100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-127700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-249000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>334100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>182100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>117100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>31600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>120000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>170300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>109000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>41300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-81800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>143800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>59500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-204300</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>82000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>45000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E38" s="2">
         <v>46109</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46018</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45927</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45836</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45745</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45654</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45563</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45472</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45381</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45290</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45108</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45017</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44835</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44744</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44653</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44464</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44282</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44191</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44009</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43918</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43827</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43736</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43645</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43554</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43463</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43372</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43099</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42917</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42826</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4173,8 +4258,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4217,787 +4303,806 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1719000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1988000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2031900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1443000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2090200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1922500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1940200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1355000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1586900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1662200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1803600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1381800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1607200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1529300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1566100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1107100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1456800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1863800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2276800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2387900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2596400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2579000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2621500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2012000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2451300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1620400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1079900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>548100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>648400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>584100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>680500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>553100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>532300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1304600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1175700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1111600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>830400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>668300</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>928000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>434000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>222600</v>
+      </c>
+      <c r="E42" s="3">
         <v>77000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>218900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>202500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>186600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>160500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>203000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>334700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>173600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>121000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>113800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>85100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>73100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>36400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>131400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>309600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>320100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>734600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>710200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>673100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>368000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>197500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>165700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>434100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>259300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>495900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>828500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1041400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1280700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1403400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1382500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1319500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1487700</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>699400</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>862300</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>507100</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>740500</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>684700</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>453000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>531000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>543800</v>
+      </c>
+      <c r="E43" s="3">
         <v>677700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>625400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>692800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>548500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>612300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>578500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>643700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>487000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>561000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>527400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>587800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>461200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>579700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>570400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>626500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>484300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>542800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>542200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>543700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>498000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>571900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>512400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>468400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>227700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>415400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>499200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>631300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>563400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>607100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>557500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>677700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>467800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>635100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>519800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>694800</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>504000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>673800</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>483000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>689000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1163700</v>
+      </c>
+      <c r="E44" s="3">
         <v>1014300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1149400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1261300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1222200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>949600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>998600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1127900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1039100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>902200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1055100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1195300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1187800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1071300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1238400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1261400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1178200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>977300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>929100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>928200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>803000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>759000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>866000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>887000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>773200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>736200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>904600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1012500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>988600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>817800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>914500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>994600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>890000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>761300</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>825400</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>864600</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>859900</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>791500</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>984000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1173000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>41800</v>
+      </c>
+      <c r="E45" s="3">
         <v>37800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>38300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>30300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>24100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>54400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>88700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>42700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>30900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>26500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>27000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>32700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>21300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>18400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>125000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>136000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>138100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>98800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>109000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>99800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>112800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>100600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>110800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>105600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>145500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>107300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>136700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>153400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>173000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>182400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>161400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>148600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>172300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>148000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>150000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>146300</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>151900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>136200</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>186000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>149000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3834700</v>
+      </c>
+      <c r="E46" s="3">
         <v>3887200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4189300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3753000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4198500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3789900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3900300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3604600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3447900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3359800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3639400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3394500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3473100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3324100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3631300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3440600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3577500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4217300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4567300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4632700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4378200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4208000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4276400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3907100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3857000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3375200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3448900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3386700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3654100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3594800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3696400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3693500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3550100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3548400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>3533200</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>3324400</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>3086700</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>2954500</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>3034000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>2976000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E47" s="3">
         <v>5900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4600</v>
-      </c>
-      <c r="F47" s="3">
-        <v>3000</v>
       </c>
       <c r="G47" s="3">
         <v>3000</v>
       </c>
       <c r="H47" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I47" s="3">
         <v>3100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>7800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>10600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>9700</v>
-      </c>
-      <c r="O47" s="3">
-        <v>10600</v>
       </c>
       <c r="P47" s="3">
         <v>10600</v>
       </c>
       <c r="Q47" s="3">
+        <v>10600</v>
+      </c>
+      <c r="R47" s="3">
         <v>10500</v>
-      </c>
-      <c r="R47" s="3">
-        <v>12000</v>
       </c>
       <c r="S47" s="3">
         <v>12000</v>
@@ -5005,8 +5110,8 @@
       <c r="T47" s="3">
         <v>12000</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>8</v>
+      <c r="U47" s="3">
+        <v>12000</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>8</v>
@@ -5020,8 +5125,8 @@
       <c r="Y47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Z47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
@@ -5036,287 +5141,296 @@
         <v>0</v>
       </c>
       <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="3">
         <v>34100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>44900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>45700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>69900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>69500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>86200</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>83300</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>82600</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>80100</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>21400</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>82000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>122000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2360400</v>
+      </c>
+      <c r="E48" s="3">
         <v>2370200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2211500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2189600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2105500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1859500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1849300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1846000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1845300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1865000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1951000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1963800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2036600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2089500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2020500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1915800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1985900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2080800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2097000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2120300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2155900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2253500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2426000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2327800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2409900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2491100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2601600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2578100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2402800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1039200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1079300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1130500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1141700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1186300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1215900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1240500</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1273300</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1316000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>1514000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>1564000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>990300</v>
+      </c>
+      <c r="E49" s="3">
         <v>997500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>966800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>968400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>973800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>951300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>942200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>969900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>955100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>963800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>978900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>965200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>978000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>987800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>982700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>961100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>985500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1011600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1027600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1045300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1054400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1055700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1075000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1066100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1058000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1056500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1063300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1066100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1083500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1083300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1094300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1103600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1110100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1138500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1136500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1140700</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1137900</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1124400</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>1125000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>1171000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5437,8 +5551,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5559,130 +5676,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>87100</v>
+      </c>
+      <c r="E52" s="3">
         <v>93700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>86200</v>
-      </c>
-      <c r="F52" s="3">
-        <v>80900</v>
       </c>
       <c r="G52" s="3">
         <v>80900</v>
       </c>
       <c r="H52" s="3">
+        <v>80900</v>
+      </c>
+      <c r="I52" s="3">
         <v>89800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>69800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>68300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>96400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>95900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>94100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>105500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>94700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>105500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>394900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>404100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>390200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>403000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>443700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>378400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>373400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>370300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>394800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>450600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>415500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>357100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>332100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>197600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>169200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>180600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>176300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>158000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>163900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>183900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>230100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>240100</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>236000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>235700</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>211000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>234000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5803,130 +5926,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7658800</v>
+      </c>
+      <c r="E54" s="3">
         <v>7739500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7813800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7347700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7751700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7047300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7080900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6800000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6641000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6602600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7004500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6723100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6868400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6789500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7039900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6733600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6951100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7724700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>8135600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>8176700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7961900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7887500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>8172200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7751600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7740400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7279900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7445900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7228500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>7343700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5942800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>6092000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>6155500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>6035300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>6143300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>6199000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>6028300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>5814000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>5652000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>5966000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>6067000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5969,8 +6098,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6013,740 +6143,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>556700</v>
+      </c>
+      <c r="E57" s="3">
         <v>431000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>543700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>532700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>609100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>436000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>489500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>495700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>477800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>332200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>411800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>460100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>448400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>371600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>468000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>498000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>562100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>448700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>472800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>451400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>370300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>355900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>335000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>284500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>144200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>246800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>267600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>350300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>351500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>202300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>169100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>202100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>202700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>165600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>184300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>172800</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>160900</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>147700</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>158000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>159000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>248900</v>
+      </c>
+      <c r="E58" s="3">
         <v>232400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>246700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>259000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>661800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>645700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>645000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>659600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>255100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>264700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>277500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>289500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>294000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>287000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>19900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>19200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>18600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>519600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>519400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>519200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>519000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>19700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>19500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>10400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>309300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>784400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>308400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>308000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>11000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>22300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>21900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>21100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>319000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>327700</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>320400</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>320700</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>22100</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>22600</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>22000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>117000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>205200</v>
+      </c>
+      <c r="E59" s="3">
         <v>220900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>238600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>176700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>292400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>260300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>228100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>185100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>180500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>203900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>227300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>188300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>205200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>180900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1261700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1192400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1164700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1287400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1437400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1290000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1224000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1209200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1322300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1258800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1033400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1060800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1199400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1077700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1228500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>975500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1082700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1017900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1042000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1093900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1205500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1096600</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1033900</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>989600</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>971000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>941000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1875600</v>
+      </c>
+      <c r="E60" s="3">
         <v>1826500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1995600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1840000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2285800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2133700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2221800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2092400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1573600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1467200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1678200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1610400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1593700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1493500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1749600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1709600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1745400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2255700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2429600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2260600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2113300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1584800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1676800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1553700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1486900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2092000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1775400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1736000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1591000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1200100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1273700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1241100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1563700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1587200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1710200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1590100</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>1216900</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>1159900</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>1151000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>1217000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2755000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2777000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2612000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2613200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2577300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2022400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2038700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2008300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2427100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2410600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2478600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2485400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2545500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2594900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1458900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1461300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1468900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1478100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1486500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1493200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1498400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2003400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2010300</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>1819800</v>
       </c>
       <c r="AA61" s="3">
         <v>1819800</v>
       </c>
       <c r="AB61" s="3">
+        <v>1819800</v>
+      </c>
+      <c r="AC61" s="3">
         <v>585800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>587400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>592200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>891500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>901700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>904700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>906900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>517100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>524400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>528600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>534400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>837100</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>839100</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>841000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>856000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>269900</v>
+      </c>
+      <c r="E62" s="3">
         <v>259000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>282500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>278500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>340500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>274300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>248000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>223000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>243300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>247000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>246000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>227200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>263000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>251000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1363600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1307100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1372700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1454900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1496600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1560100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1632500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1694900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1793100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1834000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1878200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1909000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1966600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1986700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1848400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>553800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>559700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>545500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>533500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>574300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>552700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>394200</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>399900</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>353400</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>364000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>396000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6867,8 +7016,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6989,8 +7141,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7111,130 +7266,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4937200</v>
+      </c>
+      <c r="E66" s="3">
         <v>4898100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4925400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4765500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5236400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4458800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4541700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4357700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4274000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4152300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4432600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4353900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4427400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4359000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4572100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4478000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4587000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5188700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5412700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5313900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5244200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5283100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5480200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5207500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5184900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4586800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4329400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4314900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4330900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2655600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2738100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2693500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2614300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2685900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2791500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>2518700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>2453900</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>2352400</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>2356000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>2469000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7277,8 +7438,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7399,8 +7561,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7521,8 +7686,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7643,8 +7811,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7765,130 +7936,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8513200</v>
+      </c>
+      <c r="E72" s="3">
         <v>8310600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8213800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7907400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7755200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7590100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7511800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7265400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7168700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7051600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7008400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6779700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6681300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6598200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6615100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>6448100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>6347300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>6274900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6298600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6129800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5987100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5872900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5947000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5827200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5866300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5994000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6292800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6009400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5878600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5979100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5996300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5925400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5805400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>5752200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>5751500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>5874000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>5770800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>5751900</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>5997000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>5956000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8009,8 +8186,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8131,8 +8311,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8253,130 +8436,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2721600</v>
+      </c>
+      <c r="E76" s="3">
         <v>2841400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2888400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2582200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2515300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2588500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2539200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2442300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2367000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2450300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2571900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2369200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2441000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2430500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2467800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2255600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2364100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2536000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2722900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2862800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2717700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2604400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2692000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2544100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2555500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2693100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3116500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2913600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3012800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3287200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3353900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3462000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3421000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3457400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3407500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>3509600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>3360100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>3299600</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>3610000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>3598000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8497,257 +8686,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E80" s="2">
         <v>46109</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46018</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45927</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45836</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45745</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45654</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45563</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45472</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45381</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45290</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45108</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45017</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44835</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44744</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44653</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44464</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44282</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44191</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44009</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43918</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43827</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43736</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43645</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43554</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43463</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43372</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43099</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42917</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42826</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>262200</v>
+      </c>
+      <c r="E81" s="3">
         <v>151600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>361600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>207500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>220400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>129000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>297400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>147900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>168600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>90700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>276600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>146900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>132100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>32300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>216500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>150500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>123400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>24400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>217700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>193300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>164700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-74100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>119800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-39100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-127700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-249000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>334100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>182100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>117100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>31600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>120000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>170300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>109000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>41300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-81800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>143800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>59500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-204300</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>82000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>45000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8790,130 +8988,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>55500</v>
+      </c>
+      <c r="E83" s="3">
         <v>42100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>54300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>55900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>54400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>42900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>56200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>58500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>58300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>43200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>55200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>53300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>54800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>42500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>55200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>53300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>54800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>60400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>56200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>55900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>57200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>62100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>60300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>61500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>63700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>68500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>68200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>66600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>66200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>69300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>72000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>69700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>70300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>75800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>72700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>73800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>72900</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>75500</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>78000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>76000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9034,8 +9236,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9156,8 +9361,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9278,8 +9486,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9400,8 +9611,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9522,130 +9736,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>339300</v>
+      </c>
+      <c r="E89" s="3">
         <v>145300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>779600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>53200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>176100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>122200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>738400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>97200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>277300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>121000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>605100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>72900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>270700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>14000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>395100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-43400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>45300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-105800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>357500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>216600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>247600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>46300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>347300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>57600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-70300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>6600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>543900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>6700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>197400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>100700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>470100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-17600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>230600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>24000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>514100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>102800</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>334200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>102300</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>618000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-11000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9688,130 +9908,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-53400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-51400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-75600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-93800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-187300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-79900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-61200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-41700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-33400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-39900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-42500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-42800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-39600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-61600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-72000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-44500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-39400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-53300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-50200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-35200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-28200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-27000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-26900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-32600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-21300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-54300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-85400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-81200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-49400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-48500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-56100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-50800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-42300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-38600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-48300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-32800</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-41900</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-59000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-60000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-87000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9932,8 +10156,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10054,130 +10281,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-204100</v>
+      </c>
+      <c r="E94" s="3">
         <v>45700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-92500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-111500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-198300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-39700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>55400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-192200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-87600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-52600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-71300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-55400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-77500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>33300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>110100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-37500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>365600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-82100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-93400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-343000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-199400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-61600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>242800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-206900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>220700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>276200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>130300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>188400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>107200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-69200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-77300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>94300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-827100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>128700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-404500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>215200</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-128500</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-224800</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>30000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>28000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10220,71 +10453,72 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>54800</v>
+      </c>
+      <c r="E96" s="3">
         <v>55200</v>
-      </c>
-      <c r="E96" s="3">
-        <v>55300</v>
       </c>
       <c r="F96" s="3">
         <v>55300</v>
       </c>
       <c r="G96" s="3">
+        <v>55300</v>
+      </c>
+      <c r="H96" s="3">
         <v>50700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>51000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>51200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>51400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>47500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>47900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>48500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>49000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>49200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>49500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-49700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-51000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-48100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-48900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-50600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-50500</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
@@ -10295,55 +10529,58 @@
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-49800</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-50700</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-51300</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-53100</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-48800</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-49100</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-50300</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-50700</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-40600</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-40700</v>
-      </c>
-      <c r="AK96" s="3">
-        <v>-40600</v>
       </c>
       <c r="AL96" s="3">
         <v>-40600</v>
       </c>
       <c r="AM96" s="3">
+        <v>-40600</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-40500</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-40800</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-42000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-41000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10464,8 +10701,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10586,8 +10826,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10708,370 +10951,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-387000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-211200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-99300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-573300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>114100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-132800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-131300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-186300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-253600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-173800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-156700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-223100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-112000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-98300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-83300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-238600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-788600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-207400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-356200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-67800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-34300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-305800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>673100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>268600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-153800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-308200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-244800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-124600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-262600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-54100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-164400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-38800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-48900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-48800</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-61000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-149100</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-142000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-41000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>76100</v>
+      </c>
+      <c r="E101" s="3">
         <v>32700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-77700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>49900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-13100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-36100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>46400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-20000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>14400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>37400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-30600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-30000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>37400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-30600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-30000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-18100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-19200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-14300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>3300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-21300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>23200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>16000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>7600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>5700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-15000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>5100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-3200</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-18800</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>18400</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>3600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>13300</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>19900</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>11600</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-12000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-268300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-44700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>589400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-647400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>168000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-17600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>584800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-231400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-77000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-141500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>423500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-225600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>77300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-36600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>459300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-350100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-407700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-413400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-111300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-208500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>17200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-43500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>609700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-439100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>831100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>540400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>526100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-128100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>64900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-97000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>127000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>20700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-779700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>132300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>64300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>282500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>164600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-260000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>494000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-23000</v>
       </c>
     </row>
